--- a/results/abel_results_gaussian.xlsx
+++ b/results/abel_results_gaussian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:BL42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,182 +439,302 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Cu I 510.5 nm_left_y0</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_left_A</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_left_Sigma</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_left_R2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Cu I 510.5 nm_right_R</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cu I 510.5 nm_right_Eps</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Cu I 510.5 nm_right_I_raw</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Cu I 510.5 nm_right_I_smooth</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_right_y0</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_right_A</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_right_Sigma</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Cu I 510.5 nm_right_R2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_left_R</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_left_Eps</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_left_I_raw</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_left_I_smooth</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_left_y0</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_left_A</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_left_Sigma</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_left_R2</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_right_R</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_right_Eps</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_right_I_raw</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Cu I 515.3 nm_right_I_smooth</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_right_y0</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_right_A</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_right_Sigma</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Cu I 515.3 nm_right_R2</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_left_R</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_left_Eps</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_left_I_raw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_left_I_smooth</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_left_y0</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_left_A</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_left_Sigma</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_left_R2</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_right_R</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_right_Eps</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_right_I_raw</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Cu I 521.8 nm_right_I_smooth</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_right_y0</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_right_A</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_right_Sigma</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Cu I 521.8 nm_right_R2</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_left_R</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_left_Eps</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_left_I_raw</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_left_I_smooth</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm_left_y0</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm_left_A</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm_left_Sigma</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm_left_R2</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_right_R</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_right_Eps</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_right_I_raw</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Cu I 570.0 nm_right_I_smooth</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
-          <t>Cu I 578.2 nm_left_R</t>
+          <t>Cu I 570.0 nm_right_y0</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
-          <t>Cu I 578.2 nm_left_Eps</t>
+          <t>Cu I 570.0 nm_right_A</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
-          <t>Cu I 578.2 nm_left_I_raw</t>
+          <t>Cu I 570.0 nm_right_Sigma</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
-          <t>Cu I 578.2 nm_left_I_smooth</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Cu I 578.2 nm_right_R</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Cu I 578.2 nm_right_Eps</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Cu I 578.2 nm_right_I_raw</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Cu I 578.2 nm_right_I_smooth</t>
+          <t>Cu I 570.0 nm_right_R2</t>
         </is>
       </c>
     </row>
@@ -623,1219 +743,7953 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17820.54901027648</v>
+        <v>16817.43179481263</v>
       </c>
       <c r="C2" t="n">
-        <v>53.84744084820864</v>
+        <v>53.52409585011257</v>
       </c>
       <c r="D2" t="n">
-        <v>55.35552193592967</v>
+        <v>55.72412171184494</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F2" t="n">
-        <v>16286.92680379652</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G2" t="n">
-        <v>53.84744084820864</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H2" t="n">
-        <v>55.45849431917171</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5109.760848954002</v>
+        <v>14934.63409119967</v>
       </c>
       <c r="K2" t="n">
-        <v>13.56473373368289</v>
+        <v>53.52409585011257</v>
       </c>
       <c r="L2" t="n">
-        <v>14.16687396286663</v>
+        <v>55.27680536315368</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N2" t="n">
-        <v>5255.470675070236</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O2" t="n">
-        <v>13.56473373368289</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P2" t="n">
-        <v>13.7265700168403</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>8776.385652813544</v>
+        <v>4700.126000543607</v>
       </c>
       <c r="S2" t="n">
-        <v>22.38028606950794</v>
+        <v>13.44474055092497</v>
       </c>
       <c r="T2" t="n">
-        <v>23.2880952741345</v>
+        <v>14.11041857331709</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V2" t="n">
-        <v>8392.534975487006</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W2" t="n">
-        <v>22.38028606950794</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X2" t="n">
-        <v>22.61406375231553</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1117.530994829743</v>
+        <v>4816.638829074795</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.638498972604626</v>
+        <v>13.44474055092497</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.719194835384438</v>
+        <v>13.61814638837652</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD2" t="n">
-        <v>1095.867492434052</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.638498972604626</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.789343282039871</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>14502.94246904115</v>
+        <v>7788.269791938231</v>
       </c>
       <c r="AI2" t="n">
-        <v>17.63455372258793</v>
+        <v>21.49279166276932</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.67882133260544</v>
+        <v>22.45805800741375</v>
       </c>
       <c r="AK2" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" t="n">
-        <v>5325.6698783317</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>17.63455372258793</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>17.96546189786585</v>
+      <c r="AP2" t="n">
+        <v>7312.022891100726</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>21.49279166276932</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>21.65910108616811</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1297.455786445589</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.520019547189842</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.551959760973887</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>914.5608187242181</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.520019547189842</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.620326364082795</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.899</v>
+        <v>0.217</v>
       </c>
       <c r="B3" t="n">
-        <v>14223.98553680805</v>
+        <v>16404.69317368322</v>
       </c>
       <c r="C3" t="n">
-        <v>46.62656723016049</v>
+        <v>53.40439443292778</v>
       </c>
       <c r="D3" t="n">
-        <v>45.02236123615938</v>
+        <v>55.05153013730569</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6355</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F3" t="n">
-        <v>14964.62787518733</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G3" t="n">
-        <v>51.20745712167884</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H3" t="n">
-        <v>50.66639560802469</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I3" t="n">
-        <v>0.465</v>
+        <v>0.1395</v>
       </c>
       <c r="J3" t="n">
-        <v>4706.922762014512</v>
+        <v>14864.4827884278</v>
       </c>
       <c r="K3" t="n">
-        <v>13.20707261008721</v>
+        <v>53.343092874875</v>
       </c>
       <c r="L3" t="n">
-        <v>13.22388772208391</v>
+        <v>55.03826510472149</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3875</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N3" t="n">
-        <v>5016.842902338502</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O3" t="n">
-        <v>12.93372994112039</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P3" t="n">
-        <v>12.95257333525443</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.434</v>
+        <v>0.155</v>
       </c>
       <c r="R3" t="n">
-        <v>8112.227478277057</v>
+        <v>4666.367004002674</v>
       </c>
       <c r="S3" t="n">
-        <v>21.68030331702964</v>
+        <v>13.40528438552828</v>
       </c>
       <c r="T3" t="n">
-        <v>21.82276339553417</v>
+        <v>14.00334403713007</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4185</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V3" t="n">
-        <v>7869.789619951933</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W3" t="n">
-        <v>21.20918363569952</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X3" t="n">
-        <v>21.24472927898285</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.217</v>
+        <v>0.1085</v>
       </c>
       <c r="Z3" t="n">
-        <v>1108.289909532218</v>
+        <v>4792.16829143719</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.62471802807044</v>
+        <v>13.35277175382032</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.683818875652266</v>
+        <v>13.55680568119785</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4185</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD3" t="n">
-        <v>1055.641214994236</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.584654250141681</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.651426762954371</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0465</v>
+        <v>0.1705</v>
       </c>
       <c r="AH3" t="n">
-        <v>14581.64909220046</v>
+        <v>7593.774688461381</v>
       </c>
       <c r="AI3" t="n">
-        <v>17.64153369922084</v>
+        <v>21.43230680077617</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.67882133196313</v>
+        <v>22.23452268734079</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.465</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL3" t="n">
-        <v>5116.173259412669</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM3" t="n">
-        <v>16.60178226391579</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.10325481309917</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7389.420945781318</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>21.383048838106</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21.59285067368248</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1297.693782435486</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.518379966611203</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.551556739667149</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>913.2708421310479</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>3.516167181634132</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.614544474248257</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.798</v>
+        <v>0.4185</v>
       </c>
       <c r="B4" t="n">
-        <v>7507.607320847011</v>
+        <v>15794.49403792795</v>
       </c>
       <c r="C4" t="n">
-        <v>25.56258323656836</v>
+        <v>52.29806268947293</v>
       </c>
       <c r="D4" t="n">
-        <v>24.22312793034362</v>
+        <v>53.26306191898209</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2865</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F4" t="n">
-        <v>11283.12218005194</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G4" t="n">
-        <v>39.84045746867106</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H4" t="n">
-        <v>38.2933523984374</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9145</v>
+        <v>0.279</v>
       </c>
       <c r="J4" t="n">
-        <v>3836.831190989178</v>
+        <v>14897.15379692011</v>
       </c>
       <c r="K4" t="n">
-        <v>11.38438007916432</v>
+        <v>53.01981370791604</v>
       </c>
       <c r="L4" t="n">
-        <v>10.8535030775823</v>
+        <v>54.32872868206356</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7905</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N4" t="n">
-        <v>4183.280119479536</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O4" t="n">
-        <v>10.87212907978617</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P4" t="n">
-        <v>10.78114446995655</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8525</v>
+        <v>0.31</v>
       </c>
       <c r="R4" t="n">
-        <v>6689.445347896977</v>
+        <v>4475.306557047972</v>
       </c>
       <c r="S4" t="n">
-        <v>18.90493932914184</v>
+        <v>13.31337201672214</v>
       </c>
       <c r="T4" t="n">
-        <v>18.1231256067787</v>
+        <v>13.68691946656344</v>
       </c>
       <c r="U4" t="n">
-        <v>0.837</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V4" t="n">
-        <v>6598.504049897211</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W4" t="n">
-        <v>17.80699172880794</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X4" t="n">
-        <v>17.61444518768668</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.434</v>
+        <v>0.217</v>
       </c>
       <c r="Z4" t="n">
-        <v>1081.12883982641</v>
+        <v>4821.497698433096</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.576066010650957</v>
+        <v>13.23582274662241</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.579697143107402</v>
+        <v>13.37442029412534</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.837</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD4" t="n">
-        <v>943.5868995912884</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.290418694767547</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.26707065082067</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.093</v>
+        <v>0.3255</v>
       </c>
       <c r="AH4" t="n">
-        <v>14825.64549988383</v>
+        <v>7491.199391926333</v>
       </c>
       <c r="AI4" t="n">
-        <v>17.63912326163487</v>
+        <v>21.15746517855622</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.6788213300362</v>
+        <v>21.65393378310138</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9455</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL4" t="n">
-        <v>4391.816957312759</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM4" t="n">
-        <v>14.80769103668698</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN4" t="n">
-        <v>14.65980587480526</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7348.330200340744</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21.11914615051694</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21.34982314512164</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1288.321508136705</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.519074635245666</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.550347676703836</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>909.409101796374</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.515837786640553</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.597247282634632</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.6815</v>
+        <v>0.62</v>
       </c>
       <c r="B5" t="n">
-        <v>2761.737019794307</v>
+        <v>14929.86727803559</v>
       </c>
       <c r="C5" t="n">
-        <v>6.619142079480369</v>
+        <v>50.41853428536395</v>
       </c>
       <c r="D5" t="n">
-        <v>8.806895247315596</v>
+        <v>50.46400852943577</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9375</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F5" t="n">
-        <v>7047.467368939007</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G5" t="n">
-        <v>24.98416795429241</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H5" t="n">
-        <v>23.94169325025176</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I5" t="n">
-        <v>1.364</v>
+        <v>0.434</v>
       </c>
       <c r="J5" t="n">
-        <v>2759.459233002879</v>
+        <v>14368.7385497179</v>
       </c>
       <c r="K5" t="n">
-        <v>8.430822054172575</v>
+        <v>52.28958272501548</v>
       </c>
       <c r="L5" t="n">
-        <v>7.832008192307989</v>
+        <v>53.01022234927145</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1935</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N5" t="n">
-        <v>3072.513313327473</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O5" t="n">
-        <v>8.087560947984704</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P5" t="n">
-        <v>7.914948943165347</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.271</v>
+        <v>0.4495</v>
       </c>
       <c r="R5" t="n">
-        <v>4905.497505230287</v>
+        <v>4389.93963317319</v>
       </c>
       <c r="S5" t="n">
-        <v>14.38259872105119</v>
+        <v>13.12510617246928</v>
       </c>
       <c r="T5" t="n">
-        <v>13.33730362821867</v>
+        <v>13.2345713644612</v>
       </c>
       <c r="U5" t="n">
-        <v>1.271</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V5" t="n">
-        <v>4713.093516305057</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W5" t="n">
-        <v>12.89508734349586</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X5" t="n">
-        <v>12.71060985731658</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.651</v>
+        <v>0.341</v>
       </c>
       <c r="Z5" t="n">
-        <v>1038.178374113664</v>
+        <v>4623.020638334589</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.419551381868509</v>
+        <v>12.95836037895945</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.412659660619081</v>
+        <v>13.02410685533172</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.2555</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD5" t="n">
-        <v>783.6117919902731</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.856255493410781</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.714261871774533</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.1395</v>
+        <v>0.496</v>
       </c>
       <c r="AH5" t="n">
-        <v>15260.84577895027</v>
+        <v>7017.429954003718</v>
       </c>
       <c r="AI5" t="n">
-        <v>17.64822383608046</v>
+        <v>20.52701709579793</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17.67882132682465</v>
+        <v>20.63455204640703</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.426</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL5" t="n">
-        <v>3350.858065222948</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM5" t="n">
-        <v>12.41051472280261</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.31261519286191</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7080.965695824544</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20.80261153567023</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20.93412589676909</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1297.328634252101</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.52297647226403</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.54944088042339</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>903.0298407356083</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.503797118149595</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.568579546109987</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.5805</v>
+        <v>0.8215</v>
       </c>
       <c r="B6" t="n">
-        <v>687.9451317696461</v>
+        <v>13834.23162193553</v>
       </c>
       <c r="C6" t="n">
-        <v>1.173396401048514</v>
+        <v>47.68968668715196</v>
       </c>
       <c r="D6" t="n">
-        <v>2.088277881543732</v>
+        <v>46.81961500582746</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5885</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F6" t="n">
-        <v>3652.01262099397</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.54443890660009</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H6" t="n">
-        <v>12.38267376448357</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8135</v>
+        <v>0.5735</v>
       </c>
       <c r="J6" t="n">
-        <v>1768.960793624811</v>
+        <v>13915.99387143206</v>
       </c>
       <c r="K6" t="n">
-        <v>5.119627821764674</v>
+        <v>51.37864185613576</v>
       </c>
       <c r="L6" t="n">
-        <v>4.968997190442828</v>
+        <v>51.37898157066824</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5965</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N6" t="n">
-        <v>1990.78940968371</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O6" t="n">
-        <v>5.302231527035304</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P6" t="n">
-        <v>5.125140974632526</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6895</v>
+        <v>0.6045</v>
       </c>
       <c r="R6" t="n">
-        <v>3193.683135553747</v>
+        <v>4091.478158294248</v>
       </c>
       <c r="S6" t="n">
-        <v>9.052910990063898</v>
+        <v>12.66705694185158</v>
       </c>
       <c r="T6" t="n">
-        <v>8.697902941406625</v>
+        <v>12.56587813756239</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6895</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V6" t="n">
-        <v>3057.106139719129</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W6" t="n">
-        <v>8.415297993415061</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X6" t="n">
-        <v>8.170809295908583</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.868</v>
+        <v>0.4495</v>
       </c>
       <c r="Z6" t="n">
-        <v>982.6290858503095</v>
+        <v>4465.847055667052</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.255223813785248</v>
+        <v>12.62070670170641</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.191819695038843</v>
+        <v>12.60244786793911</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.674</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD6" t="n">
-        <v>604.6040244281825</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.351291123307431</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.093834029339579</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.186</v>
+        <v>0.651</v>
       </c>
       <c r="AH6" t="n">
-        <v>15939.42928763422</v>
+        <v>6577.568477588824</v>
       </c>
       <c r="AI6" t="n">
-        <v>17.69414908932152</v>
+        <v>19.65622215145572</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.67882132232847</v>
+        <v>19.40890010041398</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.891</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL6" t="n">
-        <v>2377.579447990477</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.655574257527594</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.965218890343988</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7059.11002040776</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>20.41691511510854</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20.44791564386815</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1289.42675549172</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.521705457043115</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.547022760956338</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>894.2114213224281</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.484342469258461</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.528780283330874</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.4795</v>
+        <v>1.023</v>
       </c>
       <c r="B7" t="n">
-        <v>117.2049844214941</v>
+        <v>12560.46815839789</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2822339215328761</v>
+        <v>44.10240609696713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3275581298286738</v>
+        <v>42.53548991121809</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2395</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F7" t="n">
-        <v>1572.051816013449</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G7" t="n">
-        <v>3.384814237454327</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H7" t="n">
-        <v>5.297879733435536</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2785</v>
+        <v>0.713</v>
       </c>
       <c r="J7" t="n">
-        <v>960.0343348742733</v>
+        <v>13632.35871498641</v>
       </c>
       <c r="K7" t="n">
-        <v>2.215502094257879</v>
+        <v>50.02436384950711</v>
       </c>
       <c r="L7" t="n">
-        <v>2.710302924400632</v>
+        <v>49.36786245826583</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9995</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N7" t="n">
-        <v>1138.802547249147</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O7" t="n">
-        <v>2.868835700033077</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P7" t="n">
-        <v>2.927102698071048</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.108</v>
+        <v>0.744</v>
       </c>
       <c r="R7" t="n">
-        <v>1845.638577699936</v>
+        <v>3925.558091867308</v>
       </c>
       <c r="S7" t="n">
-        <v>4.390260480943528</v>
+        <v>12.13926648090403</v>
       </c>
       <c r="T7" t="n">
-        <v>5.026580676897285</v>
+        <v>11.83716739487418</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1235</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V7" t="n">
-        <v>1685.007887238637</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W7" t="n">
-        <v>4.45239024340226</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X7" t="n">
-        <v>4.52845559562738</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.085</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>918.9984118497673</v>
+        <v>4387.257076451335</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.018262435514481</v>
+        <v>12.15489327245563</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.928750656888518</v>
+        <v>12.08456650682562</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.0925</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD7" t="n">
-        <v>433.5752722736643</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.581710786312855</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.499788604161797</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2325</v>
+        <v>0.806</v>
       </c>
       <c r="AH7" t="n">
-        <v>16959.57163351436</v>
+        <v>6214.094482581407</v>
       </c>
       <c r="AI7" t="n">
-        <v>17.72822721845196</v>
+        <v>18.51542840891307</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.67882131654768</v>
+        <v>17.95548692798303</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3715</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL7" t="n">
-        <v>1498.135557189956</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.61657983829117</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.998902133113944</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.5115</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6837.74568107736</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>19.81730026496189</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19.74110597341904</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1301.328225508604</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.523526203637158</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.545511439205256</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>883.0768337124413</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.45058717966975</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.478179456481784</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5.363</v>
+        <v>1.2245</v>
       </c>
       <c r="B8" t="n">
-        <v>14.13705324344379</v>
+        <v>11171.75786784727</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09800530783377533</v>
+        <v>40.02497331242895</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03546569483252105</v>
+        <v>37.83846381936942</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8905</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F8" t="n">
-        <v>562.7726612657849</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9794887784029546</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H8" t="n">
-        <v>1.875071593428072</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I8" t="n">
-        <v>2.728</v>
+        <v>0.868</v>
       </c>
       <c r="J8" t="n">
-        <v>467.5753301529502</v>
+        <v>12702.09593126283</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6754235628885127</v>
+        <v>47.88762448240355</v>
       </c>
       <c r="L8" t="n">
-        <v>1.323336958495642</v>
+        <v>46.74664192922968</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4025</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N8" t="n">
-        <v>575.5398537187175</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O8" t="n">
-        <v>1.208880995162233</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4744992308824</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5265</v>
+        <v>0.899</v>
       </c>
       <c r="R8" t="n">
-        <v>947.0997145438106</v>
+        <v>3549.985405525664</v>
       </c>
       <c r="S8" t="n">
-        <v>1.525129031679619</v>
+        <v>11.36864243515446</v>
       </c>
       <c r="T8" t="n">
-        <v>2.574200314006981</v>
+        <v>10.91673172339348</v>
       </c>
       <c r="U8" t="n">
-        <v>2.542</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V8" t="n">
-        <v>846.9505713930516</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W8" t="n">
-        <v>1.886040808183146</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X8" t="n">
-        <v>2.256990431015982</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.302</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>853.4941000488893</v>
+        <v>4048.982550987873</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.72233656793363</v>
+        <v>11.49049747662196</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.636483910504774</v>
+        <v>11.39156096490807</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.511</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD8" t="n">
-        <v>289.2941834127648</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8855040020501044</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.9975051186397446</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.279</v>
+        <v>0.9765</v>
       </c>
       <c r="AH8" t="n">
-        <v>18512.76993313147</v>
+        <v>5491.826901000586</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.72585038320461</v>
+        <v>17.02686605706723</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.67882130948227</v>
+        <v>16.16827766887588</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.852</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL8" t="n">
-        <v>839.8486487950177</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.963661036930261</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.824469539705636</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6549.829029184963</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19.0562374232044</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18.899863195018</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1303.897931592094</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.529643165752554</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.541884276153496</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>869.8149703824008</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.395879057332118</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.417193416376755</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.262</v>
+        <v>1.426</v>
       </c>
       <c r="B9" t="n">
-        <v>1.185940955505308</v>
+        <v>9733.188672114782</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05941403884000665</v>
+        <v>35.27727002522406</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002451726777310139</v>
+        <v>32.95691328630502</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5415</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F9" t="n">
-        <v>167.7639109830369</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3959490568576285</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5489865556074472</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1775</v>
+        <v>1.0075</v>
       </c>
       <c r="J9" t="n">
-        <v>201.8454436093667</v>
+        <v>12205.47446837624</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1840040353193765</v>
+        <v>45.21448915496756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5680878077678936</v>
+        <v>44.09946201502966</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8055</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N9" t="n">
-        <v>257.3298868161786</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3692157612677387</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6551271331348096</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.945</v>
+        <v>1.0385</v>
       </c>
       <c r="R9" t="n">
-        <v>432.0803733072983</v>
+        <v>3326.429556421013</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4166618137623053</v>
+        <v>10.56415554713501</v>
       </c>
       <c r="T9" t="n">
-        <v>1.16821721503536</v>
+        <v>10.01702696398007</v>
       </c>
       <c r="U9" t="n">
-        <v>2.976</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V9" t="n">
-        <v>361.877181962153</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5183140777306336</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9607322650709516</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.519</v>
+        <v>0.7905</v>
       </c>
       <c r="Z9" t="n">
-        <v>795.3173723577586</v>
+        <v>3800.028853335011</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38796210143742</v>
+        <v>10.77941826700427</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.328447923136872</v>
+        <v>10.71309135910394</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9295</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD9" t="n">
-        <v>180.1436021791167</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4305903529848945</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.6160238184138266</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3255</v>
+        <v>1.1315</v>
       </c>
       <c r="AH9" t="n">
-        <v>20997.54678233991</v>
+        <v>4894.43699861856</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.73017823399465</v>
+        <v>15.37915624241673</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.67882130113223</v>
+        <v>14.442790197905</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.317</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL9" t="n">
-        <v>441.7625788227247</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.8181247751676027</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.470841645298255</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7285</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6062.175445171292</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>18.14854556850128</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.94334971186272</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1293.494486236298</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.529406307925044</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.537451094412631</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>854.7386388066524</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.332011551237096</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.346319198865432</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7.161</v>
+        <v>1.6275</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06754926405554129</v>
+        <v>8305.706878071078</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04184673988684305</v>
+        <v>30.00927524721496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001121166994594913</v>
+        <v>28.10289363833425</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1925</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F10" t="n">
-        <v>41.74366037021453</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1866801931700975</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1329638735253101</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I10" t="n">
-        <v>3.627</v>
+        <v>1.1625</v>
       </c>
       <c r="J10" t="n">
-        <v>76.87132914380165</v>
+        <v>11123.07133320253</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07931491442339721</v>
+        <v>42.05032874496504</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2144138890916998</v>
+        <v>40.91221906707802</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2085</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N10" t="n">
-        <v>101.7654526727363</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1166029665730118</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2567326297479817</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3635</v>
+        <v>1.1935</v>
       </c>
       <c r="R10" t="n">
-        <v>175.1510579728256</v>
+        <v>2919.303773938705</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1377030313596643</v>
+        <v>9.51824108203086</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4698037141759737</v>
+        <v>8.971295621591802</v>
       </c>
       <c r="U10" t="n">
-        <v>3.3945</v>
+        <v>-0.1520428396538861</v>
       </c>
       <c r="V10" t="n">
-        <v>141.2579999131578</v>
+        <v>14.26246141297098</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1584049949829296</v>
+        <v>1.26256332477434</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3712469539080986</v>
+        <v>0.9953133186433384</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.736</v>
+        <v>0.899</v>
       </c>
       <c r="Z10" t="n">
-        <v>707.3607671712879</v>
+        <v>3643.749288193966</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.976055310844055</v>
+        <v>10.05746187014557</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.017467793832461</v>
+        <v>9.983693036793403</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.348</v>
+        <v>-0.1342598846199818</v>
       </c>
       <c r="AD10" t="n">
-        <v>103.965629180474</v>
+        <v>13.7524062729965</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1774937412630091</v>
+        <v>1.147478396661003</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3532459275822791</v>
+        <v>0.9992142687856916</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.372</v>
+        <v>1.2865</v>
       </c>
       <c r="AH10" t="n">
-        <v>22133.37940362858</v>
+        <v>4412.450831811744</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.69746464228114</v>
+        <v>13.62285663390825</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.67882129149758</v>
+        <v>12.68659299047263</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.7975</v>
+        <v>-0.1824927492844038</v>
       </c>
       <c r="AL10" t="n">
-        <v>205.5237926469015</v>
+        <v>22.64055075669815</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3360023140521944</v>
+        <v>1.210328872837544</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.6758811016419843</v>
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.8215</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5909.016267535126</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17.17846720182061</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17.04765773375239</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1309.791611323177</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.526932990405296</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.534932249748294</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>837.1428089718887</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.258760153177779</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.266127781814189</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.044499999999999</v>
+        <v>1.829</v>
       </c>
       <c r="B11" t="n">
-        <v>0.003946125406283719</v>
+        <v>6941.652400250849</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03077401248242342</v>
+        <v>24.56309251629249</v>
       </c>
       <c r="D11" t="n">
-        <v>3.615079699466688e-06</v>
+        <v>23.45794728076058</v>
       </c>
       <c r="E11" t="n">
-        <v>5.8435</v>
+        <v>-0.2809402260168544</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2072105933265</v>
+        <v>56.00506193786179</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08101774699925234</v>
+        <v>1.395957450459078</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02663996827836099</v>
+        <v>0.9967588212214668</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0765</v>
+        <v>1.302</v>
       </c>
       <c r="J11" t="n">
-        <v>30.40083863152245</v>
+        <v>10287.07224550739</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04530196899741011</v>
+        <v>39.02573388793964</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07115129003793337</v>
+        <v>37.88874168635734</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6115</v>
+        <v>-0.6764658422113938</v>
       </c>
       <c r="N11" t="n">
-        <v>42.0535990342679</v>
+        <v>55.95327120536507</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04672200779862996</v>
+        <v>1.509132639315675</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08873827825299395</v>
+        <v>0.9976664094688106</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2669.527283520598</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8.570808768041973</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.016464537006049</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V11" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3244.972400013043</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.198444267837855</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.108216056977328</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3680.279080775173</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>11.5536209473312</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10.78756227079087</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5546.514206825632</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16.02694443467163</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.93379598905206</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1301.306648212906</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.526959123892598</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.529290060308426</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>833.6891519760452</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.176605380810519</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.177256430572586</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.0305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5681.887590155963</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19.31587568864601</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.16374370882985</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4415</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9675.279609972498</v>
+      </c>
+      <c r="K12" t="n">
+        <v>35.89130680263264</v>
+      </c>
+      <c r="L12" t="n">
+        <v>34.78080211446751</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N12" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2274.092733686221</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7.451029130375185</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.969578129163769</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V12" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.1315</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2958.553449961949</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.442228478671794</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.323138877480396</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.612</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3192.813643183405</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>9.625658296415461</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>9.14349158925455</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.0385</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4997.892408180366</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.83348072559837</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.76721042740609</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1319.906515906166</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.525956273419204</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.526166718882223</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>788.8171543357764</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.076763187137466</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.063532892942155</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4554.517707948715</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14.48697660359832</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.31791163431954</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F13" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5965</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8543.695381535435</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.48356914865948</v>
+      </c>
+      <c r="L13" t="n">
+        <v>31.29835356144289</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N13" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.6275</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2028.331493382435</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6.417726594023804</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.062010933010708</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2766.350924184018</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.702891421772064</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.535864377358918</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.7825</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2561.341063916873</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.562501474279546</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>7.471754690654874</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.1315</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4791.751282177602</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.80315218499421</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.74220066524346</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1324.841239527654</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.52738880316509</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.519315551887416</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.0385</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>761.7938894092795</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.975028080920641</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.958304320266374</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.4335</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3575.051678452278</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10.41263706282483</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11.97468857727699</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F14" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7691.195767457377</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29.14996455153037</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28.19598157051098</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N14" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.7825</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1677.435428490843</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.301948295358486</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5.112670740352643</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V14" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2379.928200293596</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6.832723964483389</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.650763959420516</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2091.332303841106</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.850858848465128</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6.104324443555384</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4393.641952176115</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12.57672782962818</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.53600515878843</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1314.015331988595</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.517627515876676</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.511658419791729</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.1315</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>735.8070752676956</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.863222815079604</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.846751902420658</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2747.711465188606</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.182263756272533</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.149452586643205</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8755</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7061.178050252992</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25.93297563614691</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.17279978134268</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N15" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1458.665327997519</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.293095728633698</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.324864780447054</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V15" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4725</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2107.71588216548</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.056787165621878</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.902397087405972</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.0925</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1734.454851490482</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.344373903076695</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>4.897189282067558</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.3485</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3976.111118677654</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.45514015032366</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>11.33763923016282</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1336.820073905559</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.520057749583972</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.507527622438147</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.2245</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>708.6310142908228</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.784696333464521</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.729692497661322</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.8365</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2067.513928928607</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.796260154942826</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.825877669711012</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F16" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.0305</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6041.918231359887</v>
+      </c>
+      <c r="K16" t="n">
+        <v>22.51930487437033</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21.95555203496921</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N16" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1171.105382078661</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.291750898894728</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.533839491204476</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V16" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1920.480576414643</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.328288831089294</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.188767875483279</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.263</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1314.22165947373</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.954183175429161</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.759866032454813</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3455.460067894702</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.32148653636968</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10.16511021387379</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1329.059302784837</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.522012579093332</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.498661577379721</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>680.4737779570034</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.709030215370254</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.607961026125449</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1522.731439789771</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.166816719554164</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.964377632595588</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5422.909788703066</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19.78011222968685</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19.22356685190142</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N17" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.2165</v>
+      </c>
+      <c r="R17" t="n">
+        <v>992.380364683036</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.49662169785804</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.90254123469816</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1597.185856716876</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.523253661803021</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.425699906914337</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1017.830389987337</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.979415406194936</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.895051456563354</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3231.463393326205</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.321169572922935</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.192585272117901</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1354.34690014833</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.520488348716246</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.493926334937896</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.4105</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>651.5644466882858</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.622715094881791</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.482400675062372</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3.2395</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1097.378905917597</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.092502340972696</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.510634801173915</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4542.035397764602</v>
+      </c>
+      <c r="K18" t="n">
+        <v>16.71464313631662</v>
+      </c>
+      <c r="L18" t="n">
+        <v>16.40103458581316</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N18" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.3715</v>
+      </c>
+      <c r="R18" t="n">
+        <v>773.3326282444565</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.760014373454827</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.291832272081336</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V18" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.8135</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1374.037542092823</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.845595301752683</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.810338331500027</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>802.3226690744118</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.265506264615262</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.180866894831182</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.6585</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2870.642315836404</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.23508481827319</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.107603350228089</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1362.879964578082</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.516135868554188</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.483851424282875</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.5035</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>622.1712337504289</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.516448052263769</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.353853344788651</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3.441</v>
+      </c>
+      <c r="B19" t="n">
+        <v>773.4575289306079</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.449189975443473</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.40328353812078</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4645</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3900.948722629796</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13.88523740015517</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.07111275506489</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N19" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="R19" t="n">
+        <v>638.2375803510514</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.227995621454859</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.821728587710378</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V19" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1219.900312601849</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.223439579588472</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.247647015160066</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.7435</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>573.1928032403448</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.7341038600973667</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.551955054175499</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2513.539498374313</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.161039372055484</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.086186200275075</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1353.461028041682</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.503908448181861</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.472970632734018</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.5965</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>592.652174531586</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.395286797678745</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.223150483312447</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3.6425</v>
+      </c>
+      <c r="B20" t="n">
+        <v>532.7891710791583</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.044008414188305</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.580156732271726</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3427.835486350187</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11.1858628902407</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11.95071049760203</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N20" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.666</v>
+      </c>
+      <c r="R20" t="n">
+        <v>482.5950125747133</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.7961049142308113</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.382529532168069</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V20" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>980.3202979070866</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.581071835471519</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.671285081155889</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.8985</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>431.7437085472698</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.4463310531729721</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.104361049128671</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.8755</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2106.638008903912</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.140281660795218</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.136319233636689</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1383.685392270411</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.49362695512437</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.467228039623137</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.6895</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>562.4682567732518</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.259505647078262</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.091104444388688</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="B21" t="n">
+        <v>357.9600245628722</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7219884017476415</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9828369312948347</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2781.987449595297</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8.5351208437407</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9.844339803774496</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N21" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.8055</v>
+      </c>
+      <c r="R21" t="n">
+        <v>387.2360628010845</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5209485594150556</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.055805639365087</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V21" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.1545</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>846.9374036521147</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.080522148071662</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.225433828102246</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>295.2499507618159</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.2620851642013999</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.7268075467932906</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.9685</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1917.75892786008</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.338136919910504</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.383210266778701</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1378.789096019368</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.475452700656277</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.455138475772401</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.7825</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>546.5734428467669</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.110770517837044</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1.958500488165888</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4.0455</v>
+      </c>
+      <c r="B22" t="n">
+        <v>239.4468301511236</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5116907806425532</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5595317218934761</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F22" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8985</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2322.215087814422</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6.566206396110392</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.170623764375016</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N22" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.9605</v>
+      </c>
+      <c r="R22" t="n">
+        <v>292.0136195902255</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3194252063053249</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.7605279549421707</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.2785</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>664.4116612326678</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.588745028358198</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.780887096918262</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>206.8592732906631</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.1736018435555459</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.4693123670657108</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1650.225097860521</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.51027646318557</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.578506028145507</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1412.347171603703</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.469060113524997</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.448791512208686</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>493.885500001665</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.924808072194771</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1.804090308931881</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4.2625</v>
+      </c>
+      <c r="B23" t="n">
+        <v>143.3978636759287</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.371661268846503</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2482716583823423</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F23" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1987.03290290616</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.967932294215835</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.699874821871221</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N23" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.1155</v>
+      </c>
+      <c r="R23" t="n">
+        <v>207.7628700739447</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2043124145224171</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5271220036140764</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V23" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>542.5538915200875</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.221471293695899</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.445969159861418</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.379</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>147.1555029816273</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.1203234191543096</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.2771342785998611</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>2.1855</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1347.223473876131</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.793592731949567</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.854238197303301</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1426.963701210365</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.452633005956585</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.435493240641904</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>460.5570874114572</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.743827390392679</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1.672798858009253</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.464</v>
+      </c>
+      <c r="B24" t="n">
+        <v>85.51760333935148</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2790092535560221</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.05610539502168038</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F24" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.193</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1559.691621557458</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.628947914445981</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.290533025040554</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N24" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>158.6363225377703</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1436013581112505</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.3619020841126835</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.4955</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>458.7069066281322</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.898189430054383</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.158015530985289</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.5495</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>92.44278916870549</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.08620332249332424</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.1246183301318031</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2.2785</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1202.823710162016</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.228518418939736</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>3.296730591863754</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1422.151858718398</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.426668109322378</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.421389203000786</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>430.0224444878802</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.554103299931285</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1.543180150857585</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.6655</v>
+      </c>
+      <c r="B25" t="n">
+        <v>48.09256565162157</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2093683699921069</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.07070813533494522</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F25" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.3325</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1298.54448432931</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.730468149212499</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.209634676523597</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N25" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R25" t="n">
+        <v>108.9567519085751</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0986361206914462</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2196539444642206</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V25" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.6195</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>346.7392500823668</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.6262620244168843</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.8814153453501713</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.7045</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>58.69902857215889</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.06941822955921843</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.0267381091323404</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1009.451615243599</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2.618709314003539</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.717880319365087</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1462.800006670991</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.418364182602995</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3.414035032292418</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>400.0022109734361</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.370302482654665</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1.415838217004773</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="B26" t="n">
+        <v>23.82673066511367</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1599970208859718</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.1525119806960982</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F26" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.4875</v>
+      </c>
+      <c r="J26" t="n">
+        <v>993.8522772387524</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.989016897716835</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.197652060981242</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N26" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.5495</v>
+      </c>
+      <c r="R26" t="n">
+        <v>79.58271354468376</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.07747557324580384</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1220750757227765</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V26" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>273.5644775146145</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.4427711943506873</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.6805746581274554</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.8595</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>36.88108814591165</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.05466999233163086</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-0.04226519793239925</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.4955</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>832.628183179747</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>2.046432784967148</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.212442554103767</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1465.020059702719</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>3.39746295935121</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.398722408926119</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.263</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>370.6255402858579</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.201605294829363</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1.291321998090857</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5.0685</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8.379873323217694</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1290808237736593</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.2041027114899693</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="J27" t="n">
+        <v>784.4819659384062</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.504427956364886</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.439159140798823</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N27" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.7045</v>
+      </c>
+      <c r="R27" t="n">
+        <v>51.18679974102745</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.06056725496977609</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.04060903302614441</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V27" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.8365</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>223.7275442199697</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.3159253648930264</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5136298737930571</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>18.29720122022128</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.04831063198871112</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.09389247269564817</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>653.5294438363011</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.535210017703528</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.775589120449516</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1511.322082654165</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3.390723081796491</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>3.390763965357451</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>2.356</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>342.0172025813652</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.051957855897716</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1.170122813635685</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-1.311288300701806</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1023467243475379</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.2359169298032043</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F28" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.7665</v>
+      </c>
+      <c r="J28" t="n">
+        <v>635.022486344197</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.152702643847432</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.807848994609659</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N28" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="R28" t="n">
+        <v>34.60141351528153</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.05158209443566634</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.01358132302334739</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V28" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.9605</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>161.6805635469459</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.2116010570135051</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.3588619098764443</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4.185</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>7.837914141887228</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.04173399307583109</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.1251227096626784</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>2.697</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>565.682659030189</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.182676492037603</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.451549474685292</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1537.82502186869</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.376533508904295</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>3.374242838067744</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>314.3086705968868</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0.9188099540717439</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1.052672765652315</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5.4715</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-7.347793020075096</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.08138501506790931</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.2551026072762035</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F29" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.9215</v>
+      </c>
+      <c r="J29" t="n">
+        <v>463.8140204537849</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8848024461660982</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.235980711425896</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N29" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="R29" t="n">
+        <v>19.21381013615815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0436263058202975</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.05747826126296081</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V29" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>121.9556209487741</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.1542789978321939</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.2503898247930483</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4.3555</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-0.4346029452817802</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.04474409179529346</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>-0.1475920939848355</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2.8055</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>456.6260270635967</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.8451684171336953</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.127064071875876</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.6819999999999999</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1544.883813010115</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>3.358971278807978</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.35691609012872</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>287.6681789450843</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0.8016842969709249</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0.9393440474385084</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5.673</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-11.13261809298416</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.06902303206313448</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.2664184777682033</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F30" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.061</v>
+      </c>
+      <c r="J30" t="n">
+        <v>348.4876714209748</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7504683470286957</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.8212059993621561</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N30" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.1385</v>
+      </c>
+      <c r="R30" t="n">
+        <v>10.28195438853435</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.03266356121170305</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.08580722473052124</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V30" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.1775</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>95.19061705854617</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.112909398237901</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.1631077736848182</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.5105</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-5.300225730701601</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.03312474370019666</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>-0.1606591109492456</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>360.6253919732897</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.5941487663794038</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.8544410281937307</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1604.331521259877</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.35145329907497</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3.347950621196446</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>261.723445838567</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.6911295008375981</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.8304491070888567</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5.8745</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-13.58024476451913</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.05768279255742888</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.2729467340833521</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.2005</v>
+      </c>
+      <c r="J31" t="n">
+        <v>267.2451156778737</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.6518124005515484</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4864094244911203</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N31" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.2935</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.272819255104744</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.02879361804369553</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.1080831547619721</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V31" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.3015</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>63.88442979648635</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.08179132954890429</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.084919710002753</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.6655</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-8.399997749930673</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.03211000838492652</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-0.1690559446093888</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>3.0225</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>268.5180585003823</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.4179245759840142</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.6275957802893186</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.7285</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1624.586528632134</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>3.336874854495314</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3.32941552001364</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>245.2434316576247</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.5883776106050961</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.7262416035374248</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.076</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-15.27531962698175</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.05390271589079185</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.2766309392258675</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F32" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.3555</v>
+      </c>
+      <c r="J32" t="n">
+        <v>178.6122249241931</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.5133398759054655</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1926707698917224</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N32" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-2.436909376262685</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.02990609045039206</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.1220356802551961</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V32" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>44.14587764294917</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.0611198973505775</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.03196956671859097</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>4.836</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-10.90570459231167</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.0301154319042035</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.1747631632159041</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>3.1155</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>222.1694318404967</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.3114780163054229</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.4651198610571569</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1696.962589806883</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3.324176341069374</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>3.319845898764243</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>2.8365</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>207.5484003077041</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.4877578323603232</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.6108497232647341</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.2775</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-16.58826808002967</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.05150167410986627</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.2786649951295954</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F33" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.495</v>
+      </c>
+      <c r="J33" t="n">
+        <v>124.8544400929938</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.4059002458832087</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.01368428358957352</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N33" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.588</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-6.592469617008573</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.02726702948858122</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-0.1326896980126007</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V33" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.5185</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>30.88730717455535</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.0472311874933665</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.009310840942249834</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-12.56717239471258</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.03010541177069783</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>-0.1778968702655739</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>168.5003546598874</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.2258751061523353</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.3079117765872136</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1752.76853483682</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.298174700324069</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>3.300102543349681</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>2.9295</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>182.7284308498613</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.409034572923589</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.5173996414813018</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-17.75726901686876</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.04792901494098433</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.2797637129064542</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F34" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J34" t="n">
+        <v>70.08552361810005</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.3169292915469448</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.1909305824146262</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N34" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.7275</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-9.206395168423468</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0261567825582466</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.1391683796525902</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V34" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.6425</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>16.19067486740589</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.03387435502546857</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.04507471824882289</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>5.146</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-13.86772829200181</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.02936234809836302</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.1798045695695213</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3.3325</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>116.4881383265213</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.1695219694894214</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.1805986130466613</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1794.652755801923</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.28623763712987</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>3.279553743306906</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>3.0225</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>160.3461138412462</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0.3418404091146469</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0.4290752533643419</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.6805</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-18.94607111300152</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.04499775781314699</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.2803444002414075</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F35" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.7895</v>
+      </c>
+      <c r="J35" t="n">
+        <v>33.23980837334474</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2558242898654984</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.3128280206729216</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N35" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.8825</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-11.5893597421074</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.02365113353606799</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-0.1439738491577041</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V35" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.751</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.832005773728252</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.02789313865259638</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.06849453704356673</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5.3165</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-15.12822013640472</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.02743432621580347</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-0.1810304699761234</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>3.4255</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>89.57118717164055</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.1321161256725409</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.09166963292230024</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.8215</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1903.234287612918</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>3.277320994182054</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>3.268977316720452</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>3.1155</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>138.8281333483993</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0.2793771491967742</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0.3459100229206479</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-20.28682174372544</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.03713692181980451</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.2806447018359693</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F36" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.929</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6.440586501607407</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2186165790211173</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.4064393142889592</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N36" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5.022</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-13.39236704958931</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.02246485999767273</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-0.1468116076209454</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V36" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.8595</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.2856865603001801</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.02705053164028916</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.08619601579925262</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.4715</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-16.36269164601512</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.02642975274883062</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>-0.1816664021890319</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>3.534</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>59.33597324878854</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.1009294847194107</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.007717390309576022</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1983.782382963632</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>3.249216381921736</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.247220441804416</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>118.0665061251389</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0.2283838589915303</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0.2678931574044048</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7.0835</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-21.91775227512482</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0373089491473786</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.2807966711313271</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F37" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.084</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-21.50017436265086</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.1885263782153544</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.4844093344758811</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N37" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5.177</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-15.25848997484229</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.01992843634342457</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-0.1488567517253174</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V37" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3.9835</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-6.802079095038166</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.02248307875087174</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.1010374297749959</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.642</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>-17.79595887436863</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.04241751453345678</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>-0.1820599552714387</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>3.6425</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>33.46981330269381</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.08018208062382014</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>-0.05849434664058539</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>2142.345126717365</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>3.235815701849303</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>3.236040006387611</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>3.3015</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>97.88968180150641</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0.1832137598031471</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0.1949736242970482</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-24.02990913977048</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.03536179452354798</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.280871930192465</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F38" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5.2235</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-42.66879637087096</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.162944221496666</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.5363999750010956</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N38" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.3165</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-17.17090199363793</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.01831633524692682</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.1500298118679627</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V38" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4.092</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11.9683268280117</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.01945780024899584</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.1104403729524834</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>5.797</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-19.57133471752798</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.03959807525896591</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>-0.1822564535547353</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>3.751</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>9.5597074720003</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.0623506826584416</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>-0.110239029099362</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>2317.924413669999</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>3.208842434160287</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>3.21307517281457</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>3.3945</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>78.01932080572237</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0.1537843463237114</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0.1270643453828899</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7.4865</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-26.95265587283165</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.03702417752048471</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.2809084044510392</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F39" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.363</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-61.7160352211641</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1260889174657193</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.5751856042682844</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N39" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5.4715</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-19.60563349923591</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.01672203672525972</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.1508514134853918</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V39" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>4.2005</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16.56731673229296</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.01994296025324776</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.117334010743256</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>5.952</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-21.98585820600979</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.03614955031246746</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.1823658357721382</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-5.560052339044267</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.05306922505376587</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>-0.1452078695254598</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2539.366950976466</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.177916328378162</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.189305101219929</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>3.4875</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>57.97355947819978</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0.1257441505955114</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0.06404648486610209</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-31.34664717169264</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.03381547253735967</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.2809257048953484</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F40" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.518</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-85.22553929448158</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.09513347757348921</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.6065268216981284</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N40" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-23.00086593723342</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.01648158137885528</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.15130922773322</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V40" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>4.3245</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-22.39593172138867</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.01758305022935837</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-0.122930211018694</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>6.1225</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>-25.5940503499972</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.03551067325931894</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>-0.1824298944908398</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>3.9525</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-23.75514876467344</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.0441772043602695</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-0.1771645769989411</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>2947.686636259579</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>3.163128491517447</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>3.177118118724024</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>3.5805</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>36.56255860465145</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0.109191409901987</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0.005773754358258221</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7.8895</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-34.03129289835555</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.02760383628257208</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.2809337362365868</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F41" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.6575</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-99.40106152295758</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.08615159469641573</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.6267977079584123</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N41" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5.766</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-25.09475327270942</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.03410896305967293</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.1516209029201114</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V41" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-25.81595514073949</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.01727515918956084</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-0.1263619201982174</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>6.2775</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>-27.79611083294493</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.03187831694337698</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.1824601331226</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>4.061</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>-37.24544517112052</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.03388511460152597</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>-0.2015014396413209</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>3146.500921727108</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>3.134622556966871</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3.152140296498487</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>3.6735</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>20.56159289727961</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0.08655902130509276</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>-0.04792333545900468</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0.9940734911013819</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8.090999999999999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-84.20839040395583</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05365001173618748</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.2809373854105578</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.2809402260168544</v>
+      </c>
+      <c r="F42" t="n">
+        <v>56.00506193786179</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.395957450459078</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9967588212214668</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.8125</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-266.8774099765789</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.06562243091890826</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.6428481322529171</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.6764658422113938</v>
+      </c>
+      <c r="N42" t="n">
+        <v>55.95327120536507</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.509132639315675</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9976664094688106</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5.9055</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-62.32146897003322</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.02542537393142965</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-0.1517896454181442</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.1520428396538861</v>
+      </c>
+      <c r="V42" t="n">
+        <v>14.26246141297098</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.26256332477434</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.9953133186433384</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.557</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-68.40845005265183</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.01408807366941111</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-0.1290877197523785</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-0.1342598846199818</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>13.7524062729965</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.147478396661003</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.9992142687856916</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>6.4325</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-68.79671920577562</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.01436012658464346</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>-0.1824760996514924</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-0.1824927492844038</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>22.64055075669815</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.210328872837544</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.9957703970842049</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>4.1695</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-125.7430443029632</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.02628533896100601</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>-0.2198699484334141</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>-0.2699605602307671</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>21.92906164639888</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.195515616865732</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.999609100892254</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>7681.257290622396</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3.120815212329719</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>3.139349471592823</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>-1014.821691782338</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1018.373651543312</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>34.84465964182903</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.9826424538504432</v>
+      </c>
+      <c r="BE42" t="n">
         <v>3.782</v>
       </c>
-      <c r="R11" t="n">
-        <v>74.79753346741553</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.07726208822988725</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1674252173107201</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.8285</v>
-      </c>
-      <c r="V11" t="n">
-        <v>55.57899101907137</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.06764901456407298</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1213733046026887</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.953</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1123.892092868323</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.575801012779596</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.714925939368618</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.7665</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>72.72359694773365</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.08082872561510374</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.1880849781798985</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>54201.767025092</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>17.64890907601071</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>17.6788212843608</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>4.278</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>104.0452380223738</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.1619407534675333</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.2796147198655292</v>
+      <c r="BF42" t="n">
+        <v>-60.00219998107054</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.06692315086875435</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>-0.1050392647878574</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>-0.5134040625789089</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>4.133730426661703</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1.757730014263202</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0.9940734911013819</v>
       </c>
     </row>
   </sheetData>
